--- a/Receipe_Data.xlsx
+++ b/Receipe_Data.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\James\Programming\Repository\Cooking_Website_02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\James\Programming\01 - Working\Cooking_Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F724083-85A7-45D7-A3A4-FA4EECBAADA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E577A1-4DA1-4C89-A3C4-826ECD47FA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="324">
   <si>
     <t>Maureen’s pavlova</t>
   </si>
@@ -2123,6 +2134,32 @@
   <si>
     <t>Heat oil and add onions, ginger, garlic, paprika, cayenne, fenugreek, and pepper. Mix lemon juice and a little water to make a smooth paste; add to onions and fry for 5 minutes.
 Add potatoes, turnip, and carrots; fry for 5 minutes stirring constantly. Stir in tomatoes, beans, peas, and turmeric. Bring to boil, reduce heat, cover, and simmer 25 minutes.</t>
+  </si>
+  <si>
+    <t>A-B-C Soup</t>
+  </si>
+  <si>
+    <t>Cynthia Ang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5kg chicken with bone (chicken drum-sticks)
+1 bulb of garlic
+300 to 400g potato
+300 to 400g tomato
+300 to 400g brown onion
+300 to 400g carrot
+salt or soya sauce to taste
+</t>
+  </si>
+  <si>
+    <t>Bring small pot of water to boil.
+Blanch the chicken (wash gunk off).
+Put blanched chicken into big pot.
+Fill big pot to half way to let it come to boil.
+Peal and cut vegitables into large chunks.
+Throw everything into big pot and top up water.
+*if using thermal pot, simmer for &gt;5minutes, with final minute with the lid on.
+*leave in thermal pot between 2hours until overnight</t>
   </si>
 </sst>
 </file>
@@ -2443,7 +2480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultColWidth="78.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.36328125" style="1" bestFit="1" customWidth="1"/>
@@ -2491,7 +2528,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="203" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2511,7 +2548,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2571,7 +2608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2611,7 +2648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2631,7 +2668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="145" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2651,7 +2688,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2671,7 +2708,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2691,7 +2728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="203" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2711,7 +2748,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="145" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2731,7 +2768,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2751,7 +2788,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2771,7 +2808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="174" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2791,7 +2828,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="174" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="290" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2811,7 +2848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2828,7 +2865,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2845,7 +2882,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2862,7 +2899,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2882,7 +2919,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="174" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="290" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2902,7 +2939,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2922,7 +2959,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2942,7 +2979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2962,7 +2999,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="145" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="203" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2982,7 +3019,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3002,7 +3039,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3022,7 +3059,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3039,7 +3076,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3056,7 +3093,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3073,7 +3110,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="145" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3090,7 +3127,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="232" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3107,7 +3144,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3127,7 +3164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3144,7 +3181,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="203" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3161,7 +3198,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3178,7 +3215,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3198,7 +3235,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="203" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3218,7 +3255,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="203" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3238,7 +3275,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3258,7 +3295,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3278,7 +3315,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3295,7 +3332,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3312,7 +3349,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3332,7 +3369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3352,7 +3389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3372,7 +3409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3389,7 +3426,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -3406,7 +3443,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3423,7 +3460,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3440,7 +3477,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="232" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -3457,7 +3494,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -3474,7 +3511,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -3491,7 +3528,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3508,7 +3545,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3525,7 +3562,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3542,7 +3579,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -3559,7 +3596,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -3579,7 +3616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -3596,7 +3633,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -3613,7 +3650,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3633,7 +3670,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3653,7 +3690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3670,7 +3707,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3687,7 +3724,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3707,7 +3744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3727,7 +3764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -3747,7 +3784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -3767,7 +3804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3784,7 +3821,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3801,7 +3838,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3821,7 +3858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3838,7 +3875,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3855,7 +3892,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3872,7 +3909,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3889,7 +3926,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3906,7 +3943,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3923,7 +3960,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3940,7 +3977,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -3957,7 +3994,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3974,7 +4011,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3991,7 +4028,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -4011,7 +4048,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -4028,7 +4065,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -4045,7 +4082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -4062,7 +4099,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -4079,7 +4116,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -4096,7 +4133,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -4113,7 +4150,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -4130,7 +4167,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -4150,7 +4187,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -4167,7 +4204,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -4187,7 +4224,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -4204,7 +4241,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -4221,7 +4258,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4238,7 +4275,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -4258,7 +4295,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -4276,6 +4313,26 @@
       </c>
       <c r="F99" s="1" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/Receipe_Data.xlsx
+++ b/Receipe_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\James\Programming\01 - Working\Cooking_Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E577A1-4DA1-4C89-A3C4-826ECD47FA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1ED3650-9517-4C68-9B6D-BB4C980C8C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2136,9 +2136,6 @@
 Add potatoes, turnip, and carrots; fry for 5 minutes stirring constantly. Stir in tomatoes, beans, peas, and turmeric. Bring to boil, reduce heat, cover, and simmer 25 minutes.</t>
   </si>
   <si>
-    <t>A-B-C Soup</t>
-  </si>
-  <si>
     <t>Cynthia Ang</t>
   </si>
   <si>
@@ -2160,6 +2157,9 @@
 Throw everything into big pot and top up water.
 *if using thermal pot, simmer for &gt;5minutes, with final minute with the lid on.
 *leave in thermal pot between 2hours until overnight</t>
+  </si>
+  <si>
+    <t>ABC Soup</t>
   </si>
 </sst>
 </file>
@@ -4320,19 +4320,19 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
